--- a/dama/cases/营收系统数据标准/2 服务类/2.1 基础档案数据/2.1.1 水价信息/3. 价格信息.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.1 基础档案数据/2.1.1 水价信息/3. 价格信息.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="144">
   <si>
     <t>业务属性</t>
   </si>
@@ -223,7 +223,7 @@
     <t>PRINFO_ID</t>
   </si>
   <si>
-    <t>营业收费</t>
+    <t>营业收费系统</t>
   </si>
   <si>
     <t>服务类</t>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>供排水经营管理部</t>
-  </si>
-  <si>
-    <t>营业收费系统</t>
   </si>
   <si>
     <t>信息和网络安全管理中心</t>
@@ -1175,7 +1172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1195,8 +1192,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1599,32 +1602,32 @@
       <c r="L1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="8" t="s">
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="13" t="s">
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="16" t="s">
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="18" t="s">
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="19"/>
+      <c r="AD1" s="21"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="22" customHeight="1" spans="1:30">
       <c r="A2" s="4" t="s">
@@ -1660,61 +1663,61 @@
       <c r="K2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="X2" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="Z2" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AA2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="AB2" s="20" t="s">
+      <c r="AB2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="21" t="s">
+      <c r="AC2" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="21" t="s">
+      <c r="AD2" s="23" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1752,61 +1755,61 @@
       <c r="K3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="10" t="s">
+      <c r="T3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="U3" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="W3" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="15" t="s">
+      <c r="X3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="20" t="s">
+      <c r="Z3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="AA3" s="20" t="s">
+      <c r="AA3" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="20" t="s">
+      <c r="AB3" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="AC3" s="21" t="s">
+      <c r="AC3" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AD3" s="23" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1851,16 +1854,16 @@
         <v>75</v>
       </c>
       <c r="N4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="P4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -1872,45 +1875,45 @@
         <v>75</v>
       </c>
       <c r="U4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="X4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X4" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>69</v>
@@ -1925,10 +1928,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>75</v>
@@ -1943,16 +1946,16 @@
         <v>75</v>
       </c>
       <c r="N5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="P5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -1964,45 +1967,45 @@
         <v>75</v>
       </c>
       <c r="U5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V5" s="5" t="s">
+      <c r="W5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="X5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Z5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z5" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="AA5" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AC5" s="5" t="s">
+      <c r="AD5" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>69</v>
@@ -2017,10 +2020,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>75</v>
@@ -2035,16 +2038,16 @@
         <v>75</v>
       </c>
       <c r="N6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O6" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="P6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="R6" s="5">
         <v>40</v>
@@ -2056,45 +2059,45 @@
         <v>75</v>
       </c>
       <c r="U6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V6" s="5" t="s">
+      <c r="W6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="X6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y6" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="Z6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="AA6" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="AB6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC6" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AC6" s="5" t="s">
+      <c r="AD6" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD6" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>69</v>
@@ -2109,10 +2112,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>75</v>
@@ -2127,16 +2130,16 @@
         <v>75</v>
       </c>
       <c r="N7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="P7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="Q7" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="R7" s="5">
         <v>22</v>
@@ -2148,45 +2151,45 @@
         <v>75</v>
       </c>
       <c r="U7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V7" s="5" t="s">
+      <c r="W7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="X7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y7" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Z7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z7" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="AA7" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AC7" s="5" t="s">
+      <c r="AD7" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>69</v>
@@ -2201,10 +2204,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>75</v>
@@ -2219,16 +2222,16 @@
         <v>75</v>
       </c>
       <c r="N8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="P8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="R8" s="5">
         <v>22</v>
@@ -2240,45 +2243,45 @@
         <v>75</v>
       </c>
       <c r="U8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V8" s="5" t="s">
+      <c r="W8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="X8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y8" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Z8" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z8" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="AA8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="AB8" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="AC8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD8" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD8" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>69</v>
@@ -2293,10 +2296,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>75</v>
@@ -2311,16 +2314,16 @@
         <v>75</v>
       </c>
       <c r="N9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O9" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O9" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="P9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="R9" s="5">
         <v>200</v>
@@ -2329,48 +2332,48 @@
         <v>75</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V9" s="5" t="s">
+      <c r="W9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="X9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y9" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="Z9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="AA9" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="AB9" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD9" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD9" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A10" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>69</v>
@@ -2385,10 +2388,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>75</v>
@@ -2403,16 +2406,16 @@
         <v>75</v>
       </c>
       <c r="N10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="P10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="R10" s="5">
         <v>22</v>
@@ -2424,45 +2427,45 @@
         <v>75</v>
       </c>
       <c r="U10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V10" s="5" t="s">
+      <c r="W10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W10" s="5" t="s">
+      <c r="X10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X10" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Z10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z10" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="AA10" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AB10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AD10" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD10" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A11" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>69</v>
@@ -2477,10 +2480,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>75</v>
@@ -2495,16 +2498,16 @@
         <v>75</v>
       </c>
       <c r="N11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="P11" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q11" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="R11" s="5">
         <v>7</v>
@@ -2516,45 +2519,45 @@
         <v>75</v>
       </c>
       <c r="U11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V11" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V11" s="5" t="s">
+      <c r="W11" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W11" s="5" t="s">
+      <c r="X11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="Z11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="AA11" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="AB11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AC11" s="5" t="s">
+      <c r="AD11" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD11" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
       <c r="A12" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>69</v>
@@ -2569,10 +2572,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>75</v>
@@ -2587,16 +2590,16 @@
         <v>75</v>
       </c>
       <c r="N12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="P12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P12" s="5" t="s">
+      <c r="Q12" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="R12" s="5">
         <v>22</v>
@@ -2608,39 +2611,40 @@
         <v>75</v>
       </c>
       <c r="U12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V12" s="5" t="s">
+      <c r="W12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="5" t="s">
+      <c r="X12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y12" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Z12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="AA12" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD12" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AD12" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AB1"/>
